--- a/news_daily/2026-09-01.xlsx
+++ b/news_daily/2026-09-01.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -884,32 +884,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -958,7 +958,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>e136e3613d7543a099f56e5a5aa4be95</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>e006492205d8d22958768470</t>
@@ -981,7 +985,7 @@
       <c r="AN2" s="2" t="inlineStr"/>
       <c r="AO2" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" s="2" t="inlineStr"/>
@@ -1023,10 +1027,22 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1553,7 +1569,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>APO</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Apollo Global Management</t>
@@ -1587,17 +1607,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1642,7 +1662,11 @@
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>f213c641850f42828e1027621ca7afc8</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>5d43cfd57981988bfc15a325</t>
@@ -1665,7 +1689,7 @@
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr"/>
@@ -1699,10 +1723,22 @@
       <c r="BF6" s="3" t="inlineStr"/>
       <c r="BG6" s="3" t="inlineStr"/>
       <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2304,32 +2340,32 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2369,7 +2405,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -2378,7 +2414,11 @@
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>6fd12c38d55547999dc4f5eacec41d0a</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>f2ed9f2726c5bb4fc4489405</t>
@@ -2401,7 +2441,7 @@
       <c r="AN10" s="2" t="inlineStr"/>
       <c r="AO10" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP10" s="2" t="inlineStr"/>
@@ -2443,10 +2483,22 @@
       </c>
       <c r="BG10" s="2" t="inlineStr"/>
       <c r="BH10" s="2" t="inlineStr"/>
-      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2991,178 +3043,202 @@
       <c r="BL13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Gartner, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-09-01T21:05:08+08:00</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Gartner Announces Gartner Supply Chain Planning Summit 2026 in London</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.022</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQOGZsMUNFNWxFNUpIQUNRMzU5SjE2ejlyTVFqeUpyS1NPYWptZ3BtQ2M0WlZEQWp1d3Z1UWZ0U0NXWXV1SFF5cXJMczg3UzNSVERtazlScHNVLWgxbTFhZjZJMERBM3lOalhvbkpRU2FjbFpObkxnRDFTRHFZbmVpVEpvTkYxVHdvcFFOdGVpTjhKY1piZUoxa1ZEMzV3NmhkMkVnWnlpVGNsQkFiQ0ZDQTFZdXdFRTJyY2hha1hicnNma2JKd01Fa2I1bw?oc=5</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Gartner</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>ee63dab84acf47d68ef0156c83ed5cf2</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>3e581c264ae14ee9969d941b</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>90920f588c0ab6478ce71648</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="2" t="inlineStr"/>
+      <c r="AM14" s="2" t="inlineStr"/>
+      <c r="AN14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>0.022</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQOGZsMUNFNWxFNUpIQUNRMzU5SjE2ejlyTVFqeUpyS1NPYWptZ3BtQ2M0WlZEQWp1d3Z1UWZ0U0NXWXV1SFF5cXJMczg3UzNSVERtazlScHNVLWgxbTFhZjZJMERBM3lOalhvbkpRU2FjbFpObkxnRDFTRHFZbmVpVEpvTkYxVHdvcFFOdGVpTjhKY1piZUoxa1ZEMzV3NmhkMkVnWnlpVGNsQkFiQ0ZDQTFZdXdFRTJyY2hha1hicnNma2JKd01Fa2I1bw?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>Gartner</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="inlineStr">
-        <is>
-          <t>3e581c264ae14ee9969d941b</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>90920f588c0ab6478ce71648</t>
-        </is>
-      </c>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr">
+      <c r="AP14" s="2" t="inlineStr"/>
+      <c r="AQ14" s="2" t="inlineStr"/>
+      <c r="AR14" s="2" t="inlineStr"/>
+      <c r="AS14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="inlineStr"/>
+      <c r="AU14" s="2" t="inlineStr"/>
+      <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
+      <c r="AX14" s="2" t="inlineStr"/>
+      <c r="AY14" s="2" t="inlineStr"/>
+      <c r="AZ14" s="2" t="inlineStr"/>
+      <c r="BA14" s="2" t="inlineStr"/>
+      <c r="BB14" s="2" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="BC14" s="3" t="inlineStr">
+      <c r="BC14" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr">
+      <c r="BD14" s="2" t="inlineStr"/>
+      <c r="BE14" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF14" s="3" t="inlineStr">
+      <c r="BF14" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BG14" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH14" s="3" t="inlineStr"/>
-      <c r="BI14" s="3" t="inlineStr"/>
-      <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr"/>
-      <c r="BL14" s="3" t="inlineStr"/>
+      <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -4306,32 +4382,32 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4371,7 +4447,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -4380,7 +4456,11 @@
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>4c67f4a409be4c92ac97dde7f5666015</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>203fe8e4a9d16be29b38ed3b</t>
@@ -4403,7 +4483,7 @@
       <c r="AN21" s="2" t="inlineStr"/>
       <c r="AO21" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP21" s="2" t="inlineStr"/>
@@ -4437,10 +4517,22 @@
       <c r="BF21" s="2" t="inlineStr"/>
       <c r="BG21" s="2" t="inlineStr"/>
       <c r="BH21" s="2" t="inlineStr"/>
-      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ21" s="2" t="inlineStr"/>
-      <c r="BK21" s="2" t="inlineStr"/>
-      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -4811,352 +4903,400 @@
       <c r="BL23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>SBUX</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Starbucks Corporation</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>2026-09-01T15:53:00+08:00</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Starbucks hires Nike veteran to lead supply chain operations</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOWVU0NUZzRGdEM3RNOWtYOUxpblVBUzlJTFJGVXI1WVl0blMtU2xTOTFtMF92MEtKVEFTdHRlUF9fQUFLVTloQ1FMN2lwTjJlUVQ4OVdmM19sd21GRmItcGhYNGU3NHhkOVVkc3B1Y2tpVGRMX3Y2bGs5eFBRRVJMTUFxWU9HcHhKbFdpb29CeVJzVHBpcmhkUGhjZHBYdkk?oc=5</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>5a51ffecea3d4e99805c90387bb0fe6f</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>c2388c2fbdab1be8ce4b2ad7</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>08698acd2ca5425b0bc4b7ea</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+      <c r="AK24" s="2" t="inlineStr"/>
+      <c r="AL24" s="2" t="inlineStr"/>
+      <c r="AM24" s="2" t="inlineStr"/>
+      <c r="AN24" s="2" t="inlineStr"/>
+      <c r="AO24" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>0.075</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="3" t="inlineStr"/>
-      <c r="R24" s="3" t="inlineStr"/>
-      <c r="S24" s="3" t="inlineStr"/>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOWVU0NUZzRGdEM3RNOWtYOUxpblVBUzlJTFJGVXI1WVl0blMtU2xTOTFtMF92MEtKVEFTdHRlUF9fQUFLVTloQ1FMN2lwTjJlUVQ4OVdmM19sd21GRmItcGhYNGU3NHhkOVVkc3B1Y2tpVGRMX3Y2bGs5eFBRRVJMTUFxWU9HcHhKbFdpb29CeVJzVHBpcmhkUGhjZHBYdkk?oc=5</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr"/>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA24" s="3" t="inlineStr"/>
-      <c r="AB24" s="3" t="inlineStr"/>
-      <c r="AC24" s="3" t="inlineStr">
-        <is>
-          <t>c2388c2fbdab1be8ce4b2ad7</t>
-        </is>
-      </c>
-      <c r="AD24" s="3" t="inlineStr">
-        <is>
-          <t>08698acd2ca5425b0bc4b7ea</t>
-        </is>
-      </c>
-      <c r="AE24" s="3" t="inlineStr"/>
-      <c r="AF24" s="3" t="inlineStr"/>
-      <c r="AG24" s="3" t="inlineStr"/>
-      <c r="AH24" s="3" t="inlineStr"/>
-      <c r="AI24" s="3" t="inlineStr"/>
-      <c r="AJ24" s="3" t="inlineStr"/>
-      <c r="AK24" s="3" t="inlineStr"/>
-      <c r="AL24" s="3" t="inlineStr"/>
-      <c r="AM24" s="3" t="inlineStr"/>
-      <c r="AN24" s="3" t="inlineStr"/>
-      <c r="AO24" s="3" t="inlineStr"/>
-      <c r="AP24" s="3" t="inlineStr"/>
-      <c r="AQ24" s="3" t="inlineStr"/>
-      <c r="AR24" s="3" t="inlineStr"/>
-      <c r="AS24" s="3" t="inlineStr"/>
-      <c r="AT24" s="3" t="inlineStr"/>
-      <c r="AU24" s="3" t="inlineStr"/>
-      <c r="AV24" s="3" t="inlineStr"/>
-      <c r="AW24" s="3" t="inlineStr">
+      <c r="AP24" s="2" t="inlineStr"/>
+      <c r="AQ24" s="2" t="inlineStr"/>
+      <c r="AR24" s="2" t="inlineStr"/>
+      <c r="AS24" s="2" t="inlineStr"/>
+      <c r="AT24" s="2" t="inlineStr"/>
+      <c r="AU24" s="2" t="inlineStr"/>
+      <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX24" s="3" t="inlineStr"/>
-      <c r="AY24" s="3" t="inlineStr"/>
-      <c r="AZ24" s="3" t="inlineStr"/>
-      <c r="BA24" s="3" t="inlineStr"/>
-      <c r="BB24" s="3" t="inlineStr">
+      <c r="AX24" s="2" t="inlineStr"/>
+      <c r="AY24" s="2" t="inlineStr"/>
+      <c r="AZ24" s="2" t="inlineStr"/>
+      <c r="BA24" s="2" t="inlineStr"/>
+      <c r="BB24" s="2" t="inlineStr">
         <is>
           <t>SBUX</t>
         </is>
       </c>
-      <c r="BC24" s="3" t="inlineStr">
+      <c r="BC24" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD24" s="3" t="inlineStr"/>
-      <c r="BE24" s="3" t="inlineStr">
+      <c r="BD24" s="2" t="inlineStr"/>
+      <c r="BE24" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF24" s="3" t="inlineStr">
+      <c r="BF24" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG24" s="3" t="inlineStr">
+      <c r="BG24" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH24" s="3" t="inlineStr"/>
-      <c r="BI24" s="3" t="inlineStr"/>
-      <c r="BJ24" s="3" t="inlineStr"/>
-      <c r="BK24" s="3" t="inlineStr"/>
-      <c r="BL24" s="3" t="inlineStr"/>
+      <c r="BH24" s="2" t="inlineStr"/>
+      <c r="BI24" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ24" s="2" t="inlineStr"/>
+      <c r="BK24" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Globe Life Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>2026-09-01T12:13:56+08:00</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Globe Life Field may be Rangers' most valuable weapon in upcoming September playoff push</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.197</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPd0ltZmtTMGFrbFlNUjd5UE1WLTY3Z1Z6RTdJSThXVTFpZW5qTUhONGctQmcxaXdwbVdDZWRpdk9UX2UyUmRMUHVaRUJHT0k2ODRPaUd6UFhORW1MMFk1d1FzWkFmelJBakVxUmJYdUN5ZTBpX08tNGVJbGRpU09VOHhjbWtVYjNsMmhRY0hhaC1QSEtybmRReHRodGtJYUI3aGFIeGVYOXhyTG90Ync?oc=5</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Dallas News</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>layoff</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>d3492df1af8d47078b0e9cd693160fb6</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>a0d71fc9795694e6a50ed0e1</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>5f48aab3309fa36adbb53e45</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+      <c r="AK25" s="2" t="inlineStr"/>
+      <c r="AL25" s="2" t="inlineStr"/>
+      <c r="AM25" s="2" t="inlineStr"/>
+      <c r="AN25" s="2" t="inlineStr"/>
+      <c r="AO25" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>0.197</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="inlineStr"/>
-      <c r="R25" s="3" t="inlineStr"/>
-      <c r="S25" s="3" t="inlineStr"/>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPd0ltZmtTMGFrbFlNUjd5UE1WLTY3Z1Z6RTdJSThXVTFpZW5qTUhONGctQmcxaXdwbVdDZWRpdk9UX2UyUmRMUHVaRUJHT0k2ODRPaUd6UFhORW1MMFk1d1FzWkFmelJBakVxUmJYdUN5ZTBpX08tNGVJbGRpU09VOHhjbWtVYjNsMmhRY0hhaC1QSEtybmRReHRodGtJYUI3aGFIeGVYOXhyTG90Ync?oc=5</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>Dallas News</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr"/>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA25" s="3" t="inlineStr"/>
-      <c r="AB25" s="3" t="inlineStr"/>
-      <c r="AC25" s="3" t="inlineStr">
-        <is>
-          <t>a0d71fc9795694e6a50ed0e1</t>
-        </is>
-      </c>
-      <c r="AD25" s="3" t="inlineStr">
-        <is>
-          <t>5f48aab3309fa36adbb53e45</t>
-        </is>
-      </c>
-      <c r="AE25" s="3" t="inlineStr"/>
-      <c r="AF25" s="3" t="inlineStr"/>
-      <c r="AG25" s="3" t="inlineStr"/>
-      <c r="AH25" s="3" t="inlineStr"/>
-      <c r="AI25" s="3" t="inlineStr"/>
-      <c r="AJ25" s="3" t="inlineStr"/>
-      <c r="AK25" s="3" t="inlineStr"/>
-      <c r="AL25" s="3" t="inlineStr"/>
-      <c r="AM25" s="3" t="inlineStr"/>
-      <c r="AN25" s="3" t="inlineStr"/>
-      <c r="AO25" s="3" t="inlineStr"/>
-      <c r="AP25" s="3" t="inlineStr"/>
-      <c r="AQ25" s="3" t="inlineStr"/>
-      <c r="AR25" s="3" t="inlineStr"/>
-      <c r="AS25" s="3" t="inlineStr"/>
-      <c r="AT25" s="3" t="inlineStr"/>
-      <c r="AU25" s="3" t="inlineStr"/>
-      <c r="AV25" s="3" t="inlineStr"/>
-      <c r="AW25" s="3" t="inlineStr">
+      <c r="AP25" s="2" t="inlineStr"/>
+      <c r="AQ25" s="2" t="inlineStr"/>
+      <c r="AR25" s="2" t="inlineStr"/>
+      <c r="AS25" s="2" t="inlineStr"/>
+      <c r="AT25" s="2" t="inlineStr"/>
+      <c r="AU25" s="2" t="inlineStr"/>
+      <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX25" s="3" t="inlineStr"/>
-      <c r="AY25" s="3" t="inlineStr"/>
-      <c r="AZ25" s="3" t="inlineStr"/>
-      <c r="BA25" s="3" t="inlineStr"/>
-      <c r="BB25" s="3" t="inlineStr">
+      <c r="AX25" s="2" t="inlineStr"/>
+      <c r="AY25" s="2" t="inlineStr"/>
+      <c r="AZ25" s="2" t="inlineStr"/>
+      <c r="BA25" s="2" t="inlineStr"/>
+      <c r="BB25" s="2" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="BC25" s="3" t="inlineStr">
+      <c r="BC25" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD25" s="3" t="inlineStr"/>
-      <c r="BE25" s="3" t="inlineStr">
+      <c r="BD25" s="2" t="inlineStr"/>
+      <c r="BE25" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF25" s="3" t="inlineStr">
+      <c r="BF25" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG25" s="3" t="inlineStr">
+      <c r="BG25" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH25" s="3" t="inlineStr"/>
-      <c r="BI25" s="3" t="inlineStr"/>
-      <c r="BJ25" s="3" t="inlineStr"/>
-      <c r="BK25" s="3" t="inlineStr"/>
-      <c r="BL25" s="3" t="inlineStr"/>
+      <c r="BH25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -6797,178 +6937,202 @@
       <c r="BL34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>NTRS</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Northern Trust Corporation</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>2026-09-01T07:01:46+08:00</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Supply chain seems to be in 'decent' shape: Northern Trust Wealth Management CIO</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.516</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1SMjhxXzc4YkxZd0hsV212aWhLTmstWWhNNUFYZ29IcjdibUVxWGJiS0ljY1NfMVNneS1DZG5jRUVvcFA4azlvS1hwQ21Ca1hLOG1ITlFfQWNDU2M?oc=5</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>foxbusiness.com</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>058072e590ab46bd8886d926f51755fe</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>9fba7ae37ec37781ffbfeb42</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>9e8a61012bfe76afc9a42edf</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+      <c r="AK35" s="2" t="inlineStr"/>
+      <c r="AL35" s="2" t="inlineStr"/>
+      <c r="AM35" s="2" t="inlineStr"/>
+      <c r="AN35" s="2" t="inlineStr"/>
+      <c r="AO35" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>0.516</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr"/>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1SMjhxXzc4YkxZd0hsV212aWhLTmstWWhNNUFYZ29IcjdibUVxWGJiS0ljY1NfMVNneS1DZG5jRUVvcFA4azlvS1hwQ21Ca1hLOG1ITlFfQWNDU2M?oc=5</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t>foxbusiness.com</t>
-        </is>
-      </c>
-      <c r="W35" s="3" t="inlineStr"/>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA35" s="3" t="inlineStr"/>
-      <c r="AB35" s="3" t="inlineStr"/>
-      <c r="AC35" s="3" t="inlineStr">
-        <is>
-          <t>9fba7ae37ec37781ffbfeb42</t>
-        </is>
-      </c>
-      <c r="AD35" s="3" t="inlineStr">
-        <is>
-          <t>9e8a61012bfe76afc9a42edf</t>
-        </is>
-      </c>
-      <c r="AE35" s="3" t="inlineStr"/>
-      <c r="AF35" s="3" t="inlineStr"/>
-      <c r="AG35" s="3" t="inlineStr"/>
-      <c r="AH35" s="3" t="inlineStr"/>
-      <c r="AI35" s="3" t="inlineStr"/>
-      <c r="AJ35" s="3" t="inlineStr"/>
-      <c r="AK35" s="3" t="inlineStr"/>
-      <c r="AL35" s="3" t="inlineStr"/>
-      <c r="AM35" s="3" t="inlineStr"/>
-      <c r="AN35" s="3" t="inlineStr"/>
-      <c r="AO35" s="3" t="inlineStr"/>
-      <c r="AP35" s="3" t="inlineStr"/>
-      <c r="AQ35" s="3" t="inlineStr"/>
-      <c r="AR35" s="3" t="inlineStr"/>
-      <c r="AS35" s="3" t="inlineStr"/>
-      <c r="AT35" s="3" t="inlineStr"/>
-      <c r="AU35" s="3" t="inlineStr"/>
-      <c r="AV35" s="3" t="inlineStr"/>
-      <c r="AW35" s="3" t="inlineStr">
+      <c r="AP35" s="2" t="inlineStr"/>
+      <c r="AQ35" s="2" t="inlineStr"/>
+      <c r="AR35" s="2" t="inlineStr"/>
+      <c r="AS35" s="2" t="inlineStr"/>
+      <c r="AT35" s="2" t="inlineStr"/>
+      <c r="AU35" s="2" t="inlineStr"/>
+      <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX35" s="3" t="inlineStr"/>
-      <c r="AY35" s="3" t="inlineStr"/>
-      <c r="AZ35" s="3" t="inlineStr"/>
-      <c r="BA35" s="3" t="inlineStr"/>
-      <c r="BB35" s="3" t="inlineStr">
+      <c r="AX35" s="2" t="inlineStr"/>
+      <c r="AY35" s="2" t="inlineStr"/>
+      <c r="AZ35" s="2" t="inlineStr"/>
+      <c r="BA35" s="2" t="inlineStr"/>
+      <c r="BB35" s="2" t="inlineStr">
         <is>
           <t>NTRS</t>
         </is>
       </c>
-      <c r="BC35" s="3" t="inlineStr">
+      <c r="BC35" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD35" s="3" t="inlineStr"/>
-      <c r="BE35" s="3" t="inlineStr">
+      <c r="BD35" s="2" t="inlineStr"/>
+      <c r="BE35" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF35" s="3" t="inlineStr">
+      <c r="BF35" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG35" s="3" t="inlineStr">
+      <c r="BG35" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH35" s="3" t="inlineStr"/>
-      <c r="BI35" s="3" t="inlineStr"/>
-      <c r="BJ35" s="3" t="inlineStr"/>
-      <c r="BK35" s="3" t="inlineStr"/>
-      <c r="BL35" s="3" t="inlineStr"/>
+      <c r="BH35" s="2" t="inlineStr"/>
+      <c r="BI35" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ35" s="2" t="inlineStr"/>
+      <c r="BK35" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -9341,13 +9505,17 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -9396,7 +9564,11 @@
         </is>
       </c>
       <c r="AA49" s="3" t="inlineStr"/>
-      <c r="AB49" s="3" t="inlineStr"/>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>619850d60437459b9ad44d0a6c73b647</t>
+        </is>
+      </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
           <t>2f3f4a24ec42bc53e02009cc</t>
@@ -9417,7 +9589,11 @@
       <c r="AL49" s="3" t="inlineStr"/>
       <c r="AM49" s="3" t="inlineStr"/>
       <c r="AN49" s="3" t="inlineStr"/>
-      <c r="AO49" s="3" t="inlineStr"/>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP49" s="3" t="inlineStr"/>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr"/>
@@ -9455,8 +9631,16 @@
       <c r="BH49" s="3" t="inlineStr"/>
       <c r="BI49" s="3" t="inlineStr"/>
       <c r="BJ49" s="3" t="inlineStr"/>
-      <c r="BK49" s="3" t="inlineStr"/>
-      <c r="BL49" s="3" t="inlineStr"/>
+      <c r="BK49" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL49" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL49"/>
@@ -9470,7 +9654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL23"/>
+  <dimension ref="A1:BL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9872,7 +10056,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>APO</t>
+        </is>
+      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Apollo Global Management</t>
@@ -9906,17 +10094,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -9961,7 +10149,11 @@
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>f213c641850f42828e1027621ca7afc8</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>5d43cfd57981988bfc15a325</t>
@@ -9984,7 +10176,7 @@
       <c r="AN2" s="3" t="inlineStr"/>
       <c r="AO2" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" s="3" t="inlineStr"/>
@@ -10018,10 +10210,22 @@
       <c r="BF2" s="3" t="inlineStr"/>
       <c r="BG2" s="3" t="inlineStr"/>
       <c r="BH2" s="3" t="inlineStr"/>
-      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -10598,178 +10802,198 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Gartner, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01T21:05:08+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Gartner Announces Gartner Supply Chain Planning Summit 2026 in London</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T20:36:00+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>West Virginia AG JB McCuskey on $17B Meta settlement: They made a very smart business decision</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>0.885</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQWjBOUkRCeDE3QzJTX1dkY3doQ3dzenJUN2RRS09zbWZTc3pXeUdFdVlLLVVvNWx6YVZ6SWRHa2lsbk9GOGtXamRNSzF0Z3VlUVp3Q0RmYS1BN01QZlQ1QVBmSEV6VGVOX25vRWdJbHFLZXNnbFhZYWJYRHNxV0FFaGVwUzQ2NzJWdkhISVVmVTFYQW84a1kxZ3l2MWtaOGNNYzloYnpmQy1UY2VQY2xwd2lzMm4yTXVMNXlxNEF3UTJLTU5rbnN0aWlMOGVoTkZ0?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>88fae1e5e3c541b2922ad722f9abace3</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>b7163cbfbf800df948961c6f</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>01cb186fdda1eb70848eda98</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>0.022</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQOGZsMUNFNWxFNUpIQUNRMzU5SjE2ejlyTVFqeUpyS1NPYWptZ3BtQ2M0WlZEQWp1d3Z1UWZ0U0NXWXV1SFF5cXJMczg3UzNSVERtazlScHNVLWgxbTFhZjZJMERBM3lOalhvbkpRU2FjbFpObkxnRDFTRHFZbmVpVEpvTkYxVHdvcFFOdGVpTjhKY1piZUoxa1ZEMzV3NmhkMkVnWnlpVGNsQkFiQ0ZDQTFZdXdFRTJyY2hha1hicnNma2JKd01Fa2I1bw?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>Gartner</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>3e581c264ae14ee9969d941b</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>90920f588c0ab6478ce71648</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
-      <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG6" s="4" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -10784,22 +11008,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T20:36:00+08:00</t>
+          <t>2026-09-01T18:53:00+08:00</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>West Virginia AG JB McCuskey on $17B Meta settlement: They made a very smart business decision</t>
+          <t>The Morning Risk Report: FTC Files Lawsuit Alleging Amazon Deceived Advertisers</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -10810,7 +11034,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>監管調查</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -10840,7 +11064,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>'-0.937</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr"/>
@@ -10854,12 +11078,12 @@
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQWjBOUkRCeDE3QzJTX1dkY3doQ3dzenJUN2RRS09zbWZTc3pXeUdFdVlLLVVvNWx6YVZ6SWRHa2lsbk9GOGtXamRNSzF0Z3VlUVp3Q0RmYS1BN01QZlQ1QVBmSEV6VGVOX25vRWdJbHFLZXNnbFhZYWJYRHNxV0FFaGVwUzQ2NzJWdkhISVVmVTFYQW84a1kxZ3l2MWtaOGNNYzloYnpmQy1UY2VQY2xwd2lzMm4yTXVMNXlxNEF3UTJLTU5rbnN0aWlMOGVoTkZ0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPRVM0cEZMZk9PbGROZEpzSk9CVGFLU2ZMWUE2UmpVWTBNZXZZei13STJZZlZqYjh2NHdhRVJBNDhaaG1Wd1JOdnhLb292MlNscmhPM1lFczljdWduQ3VyMEVTUnNMSkdSLXZFQ2RJZ1VOZnk2c0stTXFHbXl3MlR5MUVrVmZPeDN5R29WSnhVZndBRkpMZks3cHJMek1Wdkh3ZngtNkJ6ZnY0aktHUVBza0NOamFiSW1STGVaQUFMaXJIT1ZIOGdBaTNJVQ?oc=5</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>WSJ</t>
         </is>
       </c>
       <c r="W7" s="4" t="inlineStr"/>
@@ -10870,28 +11094,28 @@
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>REGULATORY_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z7" s="4" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>FTC</t>
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr"/>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>88fae1e5e3c541b2922ad722f9abace3</t>
+          <t>507ef878915b4233a8a5cf2f5f1eb63b</t>
         </is>
       </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>b7163cbfbf800df948961c6f</t>
+          <t>3ee16761ad5f1313634f648c</t>
         </is>
       </c>
       <c r="AD7" s="4" t="inlineStr">
         <is>
-          <t>01cb186fdda1eb70848eda98</t>
+          <t>714959e6841e99096a6381df</t>
         </is>
       </c>
       <c r="AE7" s="4" t="inlineStr"/>
@@ -10916,18 +11140,14 @@
       <c r="AT7" s="4" t="inlineStr"/>
       <c r="AU7" s="4" t="inlineStr"/>
       <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW7" s="4" t="inlineStr"/>
       <c r="AX7" s="4" t="inlineStr"/>
       <c r="AY7" s="4" t="inlineStr"/>
       <c r="AZ7" s="4" t="inlineStr"/>
       <c r="BA7" s="4" t="inlineStr"/>
       <c r="BB7" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="BC7" s="4" t="inlineStr">
@@ -10938,17 +11158,13 @@
       <c r="BD7" s="4" t="inlineStr"/>
       <c r="BE7" s="4" t="inlineStr">
         <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr"/>
       <c r="BG7" s="4" t="inlineStr">
         <is>
-          <t>上市公司</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH7" s="4" t="inlineStr"/>
@@ -10978,22 +11194,22 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>GoDaddy Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T18:53:00+08:00</t>
+          <t>2026-09-01T18:47:49+08:00</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>The Morning Risk Report: FTC Files Lawsuit Alleging Amazon Deceived Advertisers</t>
+          <t>GDDY Class Action Alert: GoDaddy Customer Acquisition Issues and Subsequent 14% Stock Drop Lead to Investor Securities Fraud Class Action to Recover Losses</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -11004,7 +11220,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -11034,7 +11250,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>'-0.937</t>
+          <t>'-0.952</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr"/>
@@ -11048,12 +11264,12 @@
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPRVM0cEZMZk9PbGROZEpzSk9CVGFLU2ZMWUE2UmpVWTBNZXZZei13STJZZlZqYjh2NHdhRVJBNDhaaG1Wd1JOdnhLb292MlNscmhPM1lFczljdWduQ3VyMEVTUnNMSkdSLXZFQ2RJZ1VOZnk2c0stTXFHbXl3MlR5MUVrVmZPeDN5R29WSnhVZndBRkpMZks3cHJMek1Wdkh3ZngtNkJ6ZnY0aktHUVBza0NOamFiSW1STGVaQUFMaXJIT1ZIOGdBaTNJVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxNeUtZeThJWjBFMXUxUGNaSUk3VWhiN0FHTVNMM3R3V0FnVm41MzVZWW1WOFVUbWZsZXYxak1BS2RvdFR6RmFwMEVxOFFWQkJDeDEwNW56bGp6UDNBVmg5d0t3RUNLTnZseUVSbkpVZ3g1Vzd2aElEVVZQcmRuWmlaU1ZOQzBQZHVaYWdWazIwVDgtRXRvdndXMmNLMjVKcEZwU1dOUmhEQ2JGOUlqN3EtWlVKWmRVMEU2blFMWFhqaW1GLUlEQkNDMFpoYU9xM3YzTy1IVzV4eGtmaDNOaU1QTU1NbzJzVlpXMDVyamxmbjF6dGI3ajN1SmU4eVdwWUl1ZDctUGtXT3huUVJ0bEFTV29sc2Z6N3hiTERHTTdlMm1JQXJFaTBtaklyOHJXOW1OdkJKOVJQd2V2QQ?oc=5</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr"/>
@@ -11064,28 +11280,28 @@
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z8" s="4" t="inlineStr">
         <is>
-          <t>FTC</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA8" s="4" t="inlineStr"/>
       <c r="AB8" s="4" t="inlineStr">
         <is>
-          <t>507ef878915b4233a8a5cf2f5f1eb63b</t>
+          <t>32823d32a9ae4e5eac219fd38da61585</t>
         </is>
       </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
-          <t>3ee16761ad5f1313634f648c</t>
+          <t>85821f14c81fb071da131aad</t>
         </is>
       </c>
       <c r="AD8" s="4" t="inlineStr">
         <is>
-          <t>714959e6841e99096a6381df</t>
+          <t>600f2e555edeb20cf685722a</t>
         </is>
       </c>
       <c r="AE8" s="4" t="inlineStr"/>
@@ -11110,14 +11326,18 @@
       <c r="AT8" s="4" t="inlineStr"/>
       <c r="AU8" s="4" t="inlineStr"/>
       <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX8" s="4" t="inlineStr"/>
       <c r="AY8" s="4" t="inlineStr"/>
       <c r="AZ8" s="4" t="inlineStr"/>
       <c r="BA8" s="4" t="inlineStr"/>
       <c r="BB8" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="BC8" s="4" t="inlineStr">
@@ -11128,13 +11348,17 @@
       <c r="BD8" s="4" t="inlineStr"/>
       <c r="BE8" s="4" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF8" s="4" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
       <c r="BG8" s="4" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH8" s="4" t="inlineStr"/>
@@ -11164,22 +11388,22 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>GoDaddy Inc. Class A Common Stock</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T18:47:49+08:00</t>
+          <t>2026-09-01T17:02:17+08:00</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>GDDY Class Action Alert: GoDaddy Customer Acquisition Issues and Subsequent 14% Stock Drop Lead to Investor Securities Fraud Class Action to Recover Losses</t>
+          <t>The Meta settlement is regulation by enforcement</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -11190,7 +11414,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -11220,7 +11444,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>'-0.952</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr"/>
@@ -11234,12 +11458,12 @@
       </c>
       <c r="U9" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxNeUtZeThJWjBFMXUxUGNaSUk3VWhiN0FHTVNMM3R3V0FnVm41MzVZWW1WOFVUbWZsZXYxak1BS2RvdFR6RmFwMEVxOFFWQkJDeDEwNW56bGp6UDNBVmg5d0t3RUNLTnZseUVSbkpVZ3g1Vzd2aElEVVZQcmRuWmlaU1ZOQzBQZHVaYWdWazIwVDgtRXRvdndXMmNLMjVKcEZwU1dOUmhEQ2JGOUlqN3EtWlVKWmRVMEU2blFMWFhqaW1GLUlEQkNDMFpoYU9xM3YzTy1IVzV4eGtmaDNOaU1QTU1NbzJzVlpXMDVyamxmbjF6dGI3ajN1SmU4eVdwWUl1ZDctUGtXT3huUVJ0bEFTV29sc2Z6N3hiTERHTTdlMm1JQXJFaTBtaklyOHJXOW1OdkJKOVJQd2V2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPemQxcXRNNnBkekQ0elNIblFWTUNnMXU5NThab3BKSmNrUklueElkUG9DU3pxUVhVNmp0eUFLQWprenNKMVV4blltMGlqV3RBTlE1WkZxVGZ4XzJULWFyYWU5ZDhhV2tHRl9lMnI1Qm5oZGJMeUp6dkhOeDNTclNEQjM4R3U?oc=5</t>
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Financial Times</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr"/>
@@ -11250,28 +11474,28 @@
       </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z9" s="4" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>settlement</t>
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr"/>
       <c r="AB9" s="4" t="inlineStr">
         <is>
-          <t>32823d32a9ae4e5eac219fd38da61585</t>
+          <t>61de6c58a50640bbba22ffb8dff9a97d</t>
         </is>
       </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
-          <t>85821f14c81fb071da131aad</t>
+          <t>a3037a7b03c9b6788ad9d45d</t>
         </is>
       </c>
       <c r="AD9" s="4" t="inlineStr">
         <is>
-          <t>600f2e555edeb20cf685722a</t>
+          <t>dc6d870af289865718f6cd6f</t>
         </is>
       </c>
       <c r="AE9" s="4" t="inlineStr"/>
@@ -11298,7 +11522,7 @@
       <c r="AV9" s="4" t="inlineStr"/>
       <c r="AW9" s="4" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="AX9" s="4" t="inlineStr"/>
@@ -11307,7 +11531,7 @@
       <c r="BA9" s="4" t="inlineStr"/>
       <c r="BB9" s="4" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>META</t>
         </is>
       </c>
       <c r="BC9" s="4" t="inlineStr">
@@ -11318,17 +11542,17 @@
       <c r="BD9" s="4" t="inlineStr"/>
       <c r="BE9" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
         </is>
       </c>
       <c r="BF9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="BG9" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>上市公司</t>
         </is>
       </c>
       <c r="BH9" s="4" t="inlineStr"/>
@@ -11358,22 +11582,22 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T17:02:17+08:00</t>
+          <t>2026-09-01T10:25:00+08:00</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>The Meta settlement is regulation by enforcement</t>
+          <t>How Amazon’s ‘Secret’ Ad Pricing System Worked, According to the FTC</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -11384,7 +11608,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>監管調查</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -11414,7 +11638,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr"/>
@@ -11428,12 +11652,12 @@
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPemQxcXRNNnBkekQ0elNIblFWTUNnMXU5NThab3BKSmNrUklueElkUG9DU3pxUVhVNmp0eUFLQWprenNKMVV4blltMGlqV3RBTlE1WkZxVGZ4XzJULWFyYWU5ZDhhV2tHRl9lMnI1Qm5oZGJMeUp6dkhOeDNTclNEQjM4R3U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOVnk2YUNQZkkzTTZtbEdZNWktQWhmdUNYcmhUWDNkWTk1bkQ0N21GR2hYRjYweWN6ejQwOW9HYzV4dUR5MmFpWFplYWpkLWdfd2FXQS1wOEd5TGVHXzlTWkZBRzV1bnFpajE3QXRndFBSR2pwaXY3b0VLb2xjOGlIRFFqdW5ZZFhGc3p1cWFXbHY1RXNrQ280ZTBrT2kzbWwtXzlvd3MzVW1ad3Ft?oc=5</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>Financial Times</t>
+          <t>WSJ</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr"/>
@@ -11444,28 +11668,28 @@
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>REGULATORY_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z10" s="4" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>FTC</t>
         </is>
       </c>
       <c r="AA10" s="4" t="inlineStr"/>
       <c r="AB10" s="4" t="inlineStr">
         <is>
-          <t>61de6c58a50640bbba22ffb8dff9a97d</t>
+          <t>bd3564c3d71c4f93a3ebd1306c99a214</t>
         </is>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
-          <t>a3037a7b03c9b6788ad9d45d</t>
+          <t>000b099a84f159a8a0904801</t>
         </is>
       </c>
       <c r="AD10" s="4" t="inlineStr">
         <is>
-          <t>dc6d870af289865718f6cd6f</t>
+          <t>ca3a5f8f48bcb20c0dafa0e2</t>
         </is>
       </c>
       <c r="AE10" s="4" t="inlineStr"/>
@@ -11490,18 +11714,14 @@
       <c r="AT10" s="4" t="inlineStr"/>
       <c r="AU10" s="4" t="inlineStr"/>
       <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW10" s="4" t="inlineStr"/>
       <c r="AX10" s="4" t="inlineStr"/>
       <c r="AY10" s="4" t="inlineStr"/>
       <c r="AZ10" s="4" t="inlineStr"/>
       <c r="BA10" s="4" t="inlineStr"/>
       <c r="BB10" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="BC10" s="4" t="inlineStr">
@@ -11512,17 +11732,13 @@
       <c r="BD10" s="4" t="inlineStr"/>
       <c r="BE10" s="4" t="inlineStr">
         <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF10" s="4" t="inlineStr"/>
       <c r="BG10" s="4" t="inlineStr">
         <is>
-          <t>上市公司</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH10" s="4" t="inlineStr"/>
@@ -11540,352 +11756,384 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Starbucks Corporation</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01T15:53:00+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Starbucks hires Nike veteran to lead supply chain operations</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T10:15:00+08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Intuit (INTU) Faces Class Action Over AI And Investor Disclosure Claims</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>'-0.932</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORzdZSjRjYmZrekVmb3l1OWd4VlBnckkxY3N4Q1p0SXR3dDBhclAxMm5iWHBXM09GdFo4Vk9USEJ2U1dpcjdRM2NNNF9oVGdER0x5a3V5QUgwRy1lczZfRmNTRnBUR0x5QjhfS3h3OHh2aUUtVjVkSkVkdDVScXVRcG1yem51RnJoVVVwdVFxQlE1WUJ3ZGV4ZTd6TQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>5e917f0a287648dc88fc5f15c016d128</t>
+        </is>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>b5bc59723ec44b1b60c5a5bd</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>9a42bf61fc999309b2228e3a</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr"/>
+      <c r="AF11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
+      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>0.075</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOWVU0NUZzRGdEM3RNOWtYOUxpblVBUzlJTFJGVXI1WVl0blMtU2xTOTFtMF92MEtKVEFTdHRlUF9fQUFLVTloQ1FMN2lwTjJlUVQ4OVdmM19sd21GRmItcGhYNGU3NHhkOVVkc3B1Y2tpVGRMX3Y2bGs5eFBRRVJMTUFxWU9HcHhKbFdpb29CeVJzVHBpcmhkUGhjZHBYdkk?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>c2388c2fbdab1be8ce4b2ad7</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>08698acd2ca5425b0bc4b7ea</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AS11" s="4" t="inlineStr"/>
+      <c r="AT11" s="4" t="inlineStr"/>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="BC11" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
+      <c r="BD11" s="4" t="inlineStr"/>
+      <c r="BE11" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF11" s="3" t="inlineStr">
+      <c r="BF11" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG11" s="3" t="inlineStr">
+      <c r="BG11" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr"/>
-      <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr"/>
-      <c r="BL11" s="3" t="inlineStr"/>
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Globe Life Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01T12:13:56+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Globe Life Field may be Rangers' most valuable weapon in upcoming September playoff push</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T09:01:57+08:00</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>PNR INVESTORS: Robbins Geller Rudman &amp; Dowd LLP Files Class Action Lawsuit Against Pentair plc and Announces Opportunity for Investors with Substantial Losses to Lead Class Action Lawsuit Before October 2, 2026 Deadline</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>'-0.119</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gJBVV95cUxQTm94UTdzbVRrSFZlQ3FsOHFMa1l1ZVNFS1lqYzhrVHJpR2hCeHdGVzA2UHFWZDA1bmRMVWV1WEF4Wk0yLUdsUnU0T2FaOHFBNlVJNUxwa0hFMzhFcTV3MEo3Uk9XZDMzZ3VsUk9pcVN4dmhCTmVSa05hd0tfcVZFdVR3TWxCNFpFTWhEQVNrSDIwTllpQ1hQTTVGeHdSeWdMa0sxbWdTdXBCbDl1R19wVTZvenRCbGdDbml0YzByY0s0X2MyWFBiSlNFd1N3WU9VUVVtRnc2YlNDWW5CNWZNMl9CTWxjWkd0VW1xTWEzWnU3RlNWNzB2WUVzNnBNUXBSUjdSZFhpaW93NUZ3SXdubmYxVEhENURaZGtfb2d2TmEwUjRhYjY1QmpaLTBQOEZhLXVLLXhiTklZNHU0Wkx5cUtKT21tejM3ZURNa2hhWEFYT3d5MDhwVFlDX1hBclAyX0tjUS1PMGktQmxfRW0zZ1Q4aTJ1dw?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>TMX Newsfile</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>1f24b8fd13b64cc29da60459be9b12f7</t>
+        </is>
+      </c>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>ae9ad286af8f154b2dbee171</t>
+        </is>
+      </c>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>4bc978645cd68b5cac62e4ad</t>
+        </is>
+      </c>
+      <c r="AE12" s="4" t="inlineStr"/>
+      <c r="AF12" s="4" t="inlineStr"/>
+      <c r="AG12" s="4" t="inlineStr"/>
+      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr"/>
+      <c r="AL12" s="4" t="inlineStr"/>
+      <c r="AM12" s="4" t="inlineStr"/>
+      <c r="AN12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>0.197</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPd0ltZmtTMGFrbFlNUjd5UE1WLTY3Z1Z6RTdJSThXVTFpZW5qTUhONGctQmcxaXdwbVdDZWRpdk9UX2UyUmRMUHVaRUJHT0k2ODRPaUd6UFhORW1MMFk1d1FzWkFmelJBakVxUmJYdUN5ZTBpX08tNGVJbGRpU09VOHhjbWtVYjNsMmhRY0hhaC1QSEtybmRReHRodGtJYUI3aGFIeGVYOXhyTG90Ync?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>Dallas News</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="3" t="inlineStr">
-        <is>
-          <t>a0d71fc9795694e6a50ed0e1</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>5f48aab3309fa36adbb53e45</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="BC12" s="3" t="inlineStr">
+      <c r="AP12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AR12" s="4" t="inlineStr"/>
+      <c r="AS12" s="4" t="inlineStr"/>
+      <c r="AT12" s="4" t="inlineStr"/>
+      <c r="AU12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AW12" s="4" t="inlineStr"/>
+      <c r="AX12" s="4" t="inlineStr"/>
+      <c r="AY12" s="4" t="inlineStr"/>
+      <c r="AZ12" s="4" t="inlineStr"/>
+      <c r="BA12" s="4" t="inlineStr"/>
+      <c r="BB12" s="4" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC12" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="3" t="inlineStr"/>
-      <c r="BI12" s="3" t="inlineStr"/>
-      <c r="BJ12" s="3" t="inlineStr"/>
-      <c r="BK12" s="3" t="inlineStr"/>
-      <c r="BL12" s="3" t="inlineStr"/>
+      <c r="BD12" s="4" t="inlineStr"/>
+      <c r="BE12" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF12" s="4" t="inlineStr"/>
+      <c r="BG12" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -11910,12 +12158,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T10:25:00+08:00</t>
+          <t>2026-09-01T05:45:36+08:00</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>How Amazon’s ‘Secret’ Ad Pricing System Worked, According to the FTC</t>
+          <t>FTC, 22 states sue Amazon over advertising surcharges</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -11956,7 +12204,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>'-0.951</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr"/>
@@ -11970,12 +12218,12 @@
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOVnk2YUNQZkkzTTZtbEdZNWktQWhmdUNYcmhUWDNkWTk1bkQ0N21GR2hYRjYweWN6ejQwOW9HYzV4dUR5MmFpWFplYWpkLWdfd2FXQS1wOEd5TGVHXzlTWkZBRzV1bnFpajE3QXRndFBSR2pwaXY3b0VLb2xjOGlIRFFqdW5ZZFhGc3p1cWFXbHY1RXNrQ280ZTBrT2kzbWwtXzlvd3MzVW1ad3Ft?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOdUFSYmo0OHNLcFF1VFZITTNhZEtkQUJ4SF9qa2Y1VWUyTGJnb2NyVnRQbmZuQXJyYWhGZEVpNjhLdnU0V2lvejFfZVhfX3FETnVvQmhBczVYSVduanRQTGp5bmlHZy16VUl1TjZBa3FHaWNrbUxvYmlXSUw3UzhoNDFfNXhtTTQ?oc=5</t>
         </is>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>Courthouse News</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr"/>
@@ -11997,17 +12245,17 @@
       <c r="AA13" s="4" t="inlineStr"/>
       <c r="AB13" s="4" t="inlineStr">
         <is>
-          <t>bd3564c3d71c4f93a3ebd1306c99a214</t>
+          <t>da2c4e4eb1e64944bb5885d2b253b86e</t>
         </is>
       </c>
       <c r="AC13" s="4" t="inlineStr">
         <is>
-          <t>000b099a84f159a8a0904801</t>
+          <t>d676532e6ec3df0a30cacee1</t>
         </is>
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>ca3a5f8f48bcb20c0dafa0e2</t>
+          <t>a964c576991971f973087284</t>
         </is>
       </c>
       <c r="AE13" s="4" t="inlineStr"/>
@@ -12086,22 +12334,22 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Intuit Inc.</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T10:15:00+08:00</t>
+          <t>2026-09-01T04:42:00+08:00</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Intuit (INTU) Faces Class Action Over AI And Investor Disclosure Claims</t>
+          <t>FTC and 22 states file suit accusing Amazon of secretly overcharging advertisers</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
@@ -12112,7 +12360,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>監管調查</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -12142,7 +12390,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>'-0.932</t>
+          <t>'-0.929</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr"/>
@@ -12156,12 +12404,12 @@
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORzdZSjRjYmZrekVmb3l1OWd4VlBnckkxY3N4Q1p0SXR3dDBhclAxMm5iWHBXM09GdFo4Vk9USEJ2U1dpcjdRM2NNNF9oVGdER0x5a3V5QUgwRy1lczZfRmNTRnBUR0x5QjhfS3h3OHh2aUUtVjVkSkVkdDVScXVRcG1yem51RnJoVVVwdVFxQlE1WUJ3ZGV4ZTd6TQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPQ3ZBS1Y2RDlwQWpEbEEtakRYbk0yVzJ5TjItSktiN0E1OVYzQjRTLTh6ZkxFWXZyLUJPbVVONy02akI2ZXZHeGZQUk5zZGdOTVdoWlJyQ0dCb2ZhTkFpaV9VZmlQeTdWMlFQREo2b0cyOExBcEYyQkhYVDM5RENFNE9MUGUtM1VvZmNOS0owaEpZVDVuTEtsNGMtd3RnSkdraTZLR1NhUmdncDNrbVc1TFJLdW45TU0waFFydGE5TUs4eXctMENwZmpB?oc=5</t>
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Politico</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr"/>
@@ -12172,28 +12420,28 @@
       </c>
       <c r="Y14" s="4" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>REGULATORY_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z14" s="4" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>FTC</t>
         </is>
       </c>
       <c r="AA14" s="4" t="inlineStr"/>
       <c r="AB14" s="4" t="inlineStr">
         <is>
-          <t>5e917f0a287648dc88fc5f15c016d128</t>
+          <t>9775409286524ffd9cd8eb9f50def185</t>
         </is>
       </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
-          <t>b5bc59723ec44b1b60c5a5bd</t>
+          <t>ab1b186369be1a2505407c7c</t>
         </is>
       </c>
       <c r="AD14" s="4" t="inlineStr">
         <is>
-          <t>9a42bf61fc999309b2228e3a</t>
+          <t>2677594f7ab6545f7b711ddc</t>
         </is>
       </c>
       <c r="AE14" s="4" t="inlineStr"/>
@@ -12218,18 +12466,14 @@
       <c r="AT14" s="4" t="inlineStr"/>
       <c r="AU14" s="4" t="inlineStr"/>
       <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW14" s="4" t="inlineStr"/>
       <c r="AX14" s="4" t="inlineStr"/>
       <c r="AY14" s="4" t="inlineStr"/>
       <c r="AZ14" s="4" t="inlineStr"/>
       <c r="BA14" s="4" t="inlineStr"/>
       <c r="BB14" s="4" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="BC14" s="4" t="inlineStr">
@@ -12240,17 +12484,13 @@
       <c r="BD14" s="4" t="inlineStr"/>
       <c r="BE14" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF14" s="4" t="inlineStr"/>
       <c r="BG14" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH14" s="4" t="inlineStr"/>
@@ -12280,22 +12520,22 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T09:01:57+08:00</t>
+          <t>2026-09-01T04:39:00+08:00</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>PNR INVESTORS: Robbins Geller Rudman &amp; Dowd LLP Files Class Action Lawsuit Against Pentair plc and Announces Opportunity for Investors with Substantial Losses to Lead Class Action Lawsuit Before October 2, 2026 Deadline</t>
+          <t>AG Davenport Sues Amazon with FTC and 21 States for Rigging Advertising Auctions, Reaping Billions in Illegal Profits</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -12306,7 +12546,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>監管調查</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -12336,7 +12576,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>'-0.119</t>
+          <t>'-0.937</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr"/>
@@ -12350,12 +12590,12 @@
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gJBVV95cUxQTm94UTdzbVRrSFZlQ3FsOHFMa1l1ZVNFS1lqYzhrVHJpR2hCeHdGVzA2UHFWZDA1bmRMVWV1WEF4Wk0yLUdsUnU0T2FaOHFBNlVJNUxwa0hFMzhFcTV3MEo3Uk9XZDMzZ3VsUk9pcVN4dmhCTmVSa05hd0tfcVZFdVR3TWxCNFpFTWhEQVNrSDIwTllpQ1hQTTVGeHdSeWdMa0sxbWdTdXBCbDl1R19wVTZvenRCbGdDbml0YzByY0s0X2MyWFBiSlNFd1N3WU9VUVVtRnc2YlNDWW5CNWZNMl9CTWxjWkd0VW1xTWEzWnU3RlNWNzB2WUVzNnBNUXBSUjdSZFhpaW93NUZ3SXdubmYxVEhENURaZGtfb2d2TmEwUjRhYjY1QmpaLTBQOEZhLXVLLXhiTklZNHU0Wkx5cUtKT21tejM3ZURNa2hhWEFYT3d5MDhwVFlDX1hBclAyX0tjUS1PMGktQmxfRW0zZ1Q4aTJ1dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOWFAtVXEzbGtYc085N3FfbFJLNFVrRk1BdXdvaXE2RjdpUkZINkdJeEMtUHJzbmhJRlJBbWpsMThrRnM5NVdiVkFoZlRqa3pidm9NTEEwUUJNVk9RT1dkeUJYeVdMcVlHM084Uk9RVl9mUTFkdnNBbFJNVzRqNjlFeFpRcjQ4Ykg3dTNTQmEwOHJELWpCVktuUE8zem1YRnltMFEwX0NON2N3RHpMMU05emxERDNUYy0xSDk0VlFmQ2p3ZExCZ016bS14bjNJYW9xUkpvNjExX09kNFhBUGctLXBWaEZIdEc0SGNSUXh3?oc=5</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>TMX Newsfile</t>
+          <t>Insider NJ</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr"/>
@@ -12366,28 +12606,28 @@
       </c>
       <c r="Y15" s="4" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>REGULATORY_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z15" s="4" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>FTC</t>
         </is>
       </c>
       <c r="AA15" s="4" t="inlineStr"/>
       <c r="AB15" s="4" t="inlineStr">
         <is>
-          <t>1f24b8fd13b64cc29da60459be9b12f7</t>
+          <t>5cd4dbfd7f014bd49a1ffe684b461ac1</t>
         </is>
       </c>
       <c r="AC15" s="4" t="inlineStr">
         <is>
-          <t>ae9ad286af8f154b2dbee171</t>
+          <t>3999aac56bfa9bb53b76523f</t>
         </is>
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>4bc978645cd68b5cac62e4ad</t>
+          <t>6ba3004303d164e1910e915b</t>
         </is>
       </c>
       <c r="AE15" s="4" t="inlineStr"/>
@@ -12419,7 +12659,7 @@
       <c r="BA15" s="4" t="inlineStr"/>
       <c r="BB15" s="4" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="BC15" s="4" t="inlineStr">
@@ -12454,178 +12694,190 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>NTRS</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Northern Trust Corporation</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01T07:01:46+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Supply chain seems to be in 'decent' shape: Northern Trust Wealth Management CIO</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T03:54:17+08:00</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>FTC and 22 States Sue Amazon Over Advertising Practices</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>監管調查</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>'-0.938</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr"/>
+      <c r="Q16" s="4" t="inlineStr"/>
+      <c r="R16" s="4" t="inlineStr"/>
+      <c r="S16" s="4" t="inlineStr"/>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOWlU3MmpCaE01eGNlN2wzandqZjNIQlpQdXBaUFRweTVEM3RJZi1pcHE4VWs3cjZsNnh1b3cxX1FJTkJZRU9PZmNKdUJ6RXdVMThrQXpDM09ScktoUVJtc2V6dW1iNHlOTkVTT201VFRNS0JQbDBBVlFicUROYXFiUzJpdUpBZw?oc=5</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>The New York Times</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr"/>
+      <c r="X16" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA16" s="4" t="inlineStr"/>
+      <c r="AB16" s="4" t="inlineStr">
+        <is>
+          <t>c2dd5d797110490fb8558b0b4aba1edc</t>
+        </is>
+      </c>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>f8820d0a89ac0aed2c6dc5f0</t>
+        </is>
+      </c>
+      <c r="AD16" s="4" t="inlineStr">
+        <is>
+          <t>004b1245213be0dd4574e8a2</t>
+        </is>
+      </c>
+      <c r="AE16" s="4" t="inlineStr"/>
+      <c r="AF16" s="4" t="inlineStr"/>
+      <c r="AG16" s="4" t="inlineStr"/>
+      <c r="AH16" s="4" t="inlineStr"/>
+      <c r="AI16" s="4" t="inlineStr"/>
+      <c r="AJ16" s="4" t="inlineStr"/>
+      <c r="AK16" s="4" t="inlineStr"/>
+      <c r="AL16" s="4" t="inlineStr"/>
+      <c r="AM16" s="4" t="inlineStr"/>
+      <c r="AN16" s="4" t="inlineStr"/>
+      <c r="AO16" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>0.516</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1SMjhxXzc4YkxZd0hsV212aWhLTmstWWhNNUFYZ29IcjdibUVxWGJiS0ljY1NfMVNneS1DZG5jRUVvcFA4azlvS1hwQ21Ca1hLOG1ITlFfQWNDU2M?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t>foxbusiness.com</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA16" s="3" t="inlineStr"/>
-      <c r="AB16" s="3" t="inlineStr"/>
-      <c r="AC16" s="3" t="inlineStr">
-        <is>
-          <t>9fba7ae37ec37781ffbfeb42</t>
-        </is>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>9e8a61012bfe76afc9a42edf</t>
-        </is>
-      </c>
-      <c r="AE16" s="3" t="inlineStr"/>
-      <c r="AF16" s="3" t="inlineStr"/>
-      <c r="AG16" s="3" t="inlineStr"/>
-      <c r="AH16" s="3" t="inlineStr"/>
-      <c r="AI16" s="3" t="inlineStr"/>
-      <c r="AJ16" s="3" t="inlineStr"/>
-      <c r="AK16" s="3" t="inlineStr"/>
-      <c r="AL16" s="3" t="inlineStr"/>
-      <c r="AM16" s="3" t="inlineStr"/>
-      <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr"/>
-      <c r="AP16" s="3" t="inlineStr"/>
-      <c r="AQ16" s="3" t="inlineStr"/>
-      <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="inlineStr"/>
-      <c r="AW16" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX16" s="3" t="inlineStr"/>
-      <c r="AY16" s="3" t="inlineStr"/>
-      <c r="AZ16" s="3" t="inlineStr"/>
-      <c r="BA16" s="3" t="inlineStr"/>
-      <c r="BB16" s="3" t="inlineStr">
-        <is>
-          <t>NTRS</t>
-        </is>
-      </c>
-      <c r="BC16" s="3" t="inlineStr">
+      <c r="AP16" s="4" t="inlineStr"/>
+      <c r="AQ16" s="4" t="inlineStr"/>
+      <c r="AR16" s="4" t="inlineStr"/>
+      <c r="AS16" s="4" t="inlineStr"/>
+      <c r="AT16" s="4" t="inlineStr"/>
+      <c r="AU16" s="4" t="inlineStr"/>
+      <c r="AV16" s="4" t="inlineStr"/>
+      <c r="AW16" s="4" t="inlineStr"/>
+      <c r="AX16" s="4" t="inlineStr"/>
+      <c r="AY16" s="4" t="inlineStr"/>
+      <c r="AZ16" s="4" t="inlineStr"/>
+      <c r="BA16" s="4" t="inlineStr"/>
+      <c r="BB16" s="4" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="BC16" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD16" s="3" t="inlineStr"/>
-      <c r="BE16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG16" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH16" s="3" t="inlineStr"/>
-      <c r="BI16" s="3" t="inlineStr"/>
-      <c r="BJ16" s="3" t="inlineStr"/>
-      <c r="BK16" s="3" t="inlineStr"/>
-      <c r="BL16" s="3" t="inlineStr"/>
+      <c r="BD16" s="4" t="inlineStr"/>
+      <c r="BE16" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF16" s="4" t="inlineStr"/>
+      <c r="BG16" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH16" s="4" t="inlineStr"/>
+      <c r="BI16" s="4" t="inlineStr"/>
+      <c r="BJ16" s="4" t="inlineStr"/>
+      <c r="BK16" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -12650,12 +12902,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T05:45:36+08:00</t>
+          <t>2026-09-01T03:39:49+08:00</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>FTC, 22 states sue Amazon over advertising surcharges</t>
+          <t>FTC sues Amazon, alleging it overcharged advertisers</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
@@ -12696,7 +12948,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>'-0.951</t>
+          <t>'-0.934</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr"/>
@@ -12710,12 +12962,12 @@
       </c>
       <c r="U17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOdUFSYmo0OHNLcFF1VFZITTNhZEtkQUJ4SF9qa2Y1VWUyTGJnb2NyVnRQbmZuQXJyYWhGZEVpNjhLdnU0V2lvejFfZVhfX3FETnVvQmhBczVYSVduanRQTGp5bmlHZy16VUl1TjZBa3FHaWNrbUxvYmlXSUw3UzhoNDFfNXhtTTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBLTXBWUDVyaXFnR1c0LUh4M25EYXFzUGVoYlRPYWQyZjF5alVSd2ZoaDZFcVdGaDhvRjk4d0wwRmhRSTktbzBXWER5eFJOZkMtT2tRay1qMldfRk1CM0cwTkxHa2psbzEtM1E2M29ERzlocWZS?oc=5</t>
         </is>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>Courthouse News</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr"/>
@@ -12737,17 +12989,17 @@
       <c r="AA17" s="4" t="inlineStr"/>
       <c r="AB17" s="4" t="inlineStr">
         <is>
-          <t>da2c4e4eb1e64944bb5885d2b253b86e</t>
+          <t>e0aaa3cdf81747feb03dd5a9656858c0</t>
         </is>
       </c>
       <c r="AC17" s="4" t="inlineStr">
         <is>
-          <t>d676532e6ec3df0a30cacee1</t>
+          <t>2a0a25ef1ef4370eeb5a5eaa</t>
         </is>
       </c>
       <c r="AD17" s="4" t="inlineStr">
         <is>
-          <t>a964c576991971f973087284</t>
+          <t>ad64556ce1e6d19ce0b16072</t>
         </is>
       </c>
       <c r="AE17" s="4" t="inlineStr"/>
@@ -12836,12 +13088,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01T04:42:00+08:00</t>
+          <t>2026-09-01T02:06:28+08:00</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>FTC and 22 states file suit accusing Amazon of secretly overcharging advertisers</t>
+          <t>FTC聯合22州起訴亞馬遜 涉嫌從廣吿主多收數百億美元</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
@@ -12880,28 +13132,24 @@
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>'-0.929</t>
-        </is>
-      </c>
+      <c r="O18" s="4" t="inlineStr"/>
       <c r="P18" s="4" t="inlineStr"/>
       <c r="Q18" s="4" t="inlineStr"/>
       <c r="R18" s="4" t="inlineStr"/>
       <c r="S18" s="4" t="inlineStr"/>
       <c r="T18" s="4" t="inlineStr">
         <is>
-          <t>公司清單／別名核對</t>
+          <t>主體證據不足</t>
         </is>
       </c>
       <c r="U18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPQ3ZBS1Y2RDlwQWpEbEEtakRYbk0yVzJ5TjItSktiN0E1OVYzQjRTLTh6ZkxFWXZyLUJPbVVONy02akI2ZXZHeGZQUk5zZGdOTVdoWlJyQ0dCb2ZhTkFpaV9VZmlQeTdWMlFQREo2b0cyOExBcEYyQkhYVDM5RENFNE9MUGUtM1VvZmNOS0owaEpZVDVuTEtsNGMtd3RnSkdraTZLR1NhUmdncDNrbVc1TFJLdW45TU0waFFydGE5TUs4eXctMENwZmpB?oc=5</t>
+          <t>https://www.gelonghui.com/live/2643055</t>
         </is>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>Politico</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr"/>
@@ -12923,17 +13171,17 @@
       <c r="AA18" s="4" t="inlineStr"/>
       <c r="AB18" s="4" t="inlineStr">
         <is>
-          <t>9775409286524ffd9cd8eb9f50def185</t>
+          <t>ea9af256a8ac4be09998875709baf4ca</t>
         </is>
       </c>
       <c r="AC18" s="4" t="inlineStr">
         <is>
-          <t>ab1b186369be1a2505407c7c</t>
+          <t>b66f2435d96a4a21a118e6f6</t>
         </is>
       </c>
       <c r="AD18" s="4" t="inlineStr">
         <is>
-          <t>2677594f7ab6545f7b711ddc</t>
+          <t>8143fc2d66639e2ae05eba17</t>
         </is>
       </c>
       <c r="AE18" s="4" t="inlineStr"/>
@@ -12970,23 +13218,23 @@
       </c>
       <c r="BC18" s="4" t="inlineStr">
         <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD18" s="4" t="inlineStr"/>
-      <c r="BE18" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD18" s="4" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="BE18" s="4" t="inlineStr"/>
       <c r="BF18" s="4" t="inlineStr"/>
-      <c r="BG18" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
+      <c r="BG18" s="4" t="inlineStr"/>
       <c r="BH18" s="4" t="inlineStr"/>
-      <c r="BI18" s="4" t="inlineStr"/>
+      <c r="BI18" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ18" s="4" t="inlineStr"/>
       <c r="BK18" s="4" t="inlineStr">
         <is>
@@ -13000,913 +13248,193 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01T04:39:00+08:00</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>AG Davenport Sues Amazon with FTC and 21 States for Rigging Advertising Auctions, Reaping Billions in Illegal Profits</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>CLX</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Clorox</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:18:00+08:00</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Clorox Slides as Weak Demand, Margin Pressure, and Cautious FY27 Outlook Remain in Focus</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>營運惡化</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>'-0.937</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>'-0.962</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOWFAtVXEzbGtYc085N3FfbFJLNFVrRk1BdXdvaXE2RjdpUkZINkdJeEMtUHJzbmhJRlJBbWpsMThrRnM5NVdiVkFoZlRqa3pidm9NTEEwUUJNVk9RT1dkeUJYeVdMcVlHM084Uk9RVl9mUTFkdnNBbFJNVzRqNjlFeFpRcjQ4Ykg3dTNTQmEwOHJELWpCVktuUE8zem1YRnltMFEwX0NON2N3RHpMMU05emxERDNUYy0xSDk0VlFmQ2p3ZExCZ016bS14bjNJYW9xUkpvNjExX09kNFhBUGctLXBWaEZIdEc0SGNSUXh3?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t>Insider NJ</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y19" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z19" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr">
-        <is>
-          <t>5cd4dbfd7f014bd49a1ffe684b461ac1</t>
-        </is>
-      </c>
-      <c r="AC19" s="4" t="inlineStr">
-        <is>
-          <t>3999aac56bfa9bb53b76523f</t>
-        </is>
-      </c>
-      <c r="AD19" s="4" t="inlineStr">
-        <is>
-          <t>6ba3004303d164e1910e915b</t>
-        </is>
-      </c>
-      <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="4" t="inlineStr"/>
-      <c r="AG19" s="4" t="inlineStr"/>
-      <c r="AH19" s="4" t="inlineStr"/>
-      <c r="AI19" s="4" t="inlineStr"/>
-      <c r="AJ19" s="4" t="inlineStr"/>
-      <c r="AK19" s="4" t="inlineStr"/>
-      <c r="AL19" s="4" t="inlineStr"/>
-      <c r="AM19" s="4" t="inlineStr"/>
-      <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr">
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNV05aeksyZGRMRjEyT3ZMRUZQNEJzOEN0cjBLYXVmLXA2c2xiVnVfZHQ1WkJrRVQ5Z01XMm5MakRBczB4R1FXczgxY2ZESjNKWGlfT0Y0YUhub2k5ckJsQXA3WVlqZlA2aFI1SVVBNnB4RE1XRTQxZ1R5dW9KUVpZSmRuTmpSREU0aUVnVVVYS0phdHBoZG1PTnVVMTYtaERTZWo1TUR6TUJXWW1vaVJ3XzVwUFFzRmVhLWx1RUtYcWdlZzA?oc=5</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>Quiver Quantitative</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>619850d60437459b9ad44d0a6c73b647</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>2f3f4a24ec42bc53e02009cc</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr">
+        <is>
+          <t>9cebe0a71c84871dc5c89d97</t>
+        </is>
+      </c>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP19" s="4" t="inlineStr"/>
-      <c r="AQ19" s="4" t="inlineStr"/>
-      <c r="AR19" s="4" t="inlineStr"/>
-      <c r="AS19" s="4" t="inlineStr"/>
-      <c r="AT19" s="4" t="inlineStr"/>
-      <c r="AU19" s="4" t="inlineStr"/>
-      <c r="AV19" s="4" t="inlineStr"/>
-      <c r="AW19" s="4" t="inlineStr"/>
-      <c r="AX19" s="4" t="inlineStr"/>
-      <c r="AY19" s="4" t="inlineStr"/>
-      <c r="AZ19" s="4" t="inlineStr"/>
-      <c r="BA19" s="4" t="inlineStr"/>
-      <c r="BB19" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BC19" s="4" t="inlineStr">
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr"/>
+      <c r="AS19" s="3" t="inlineStr"/>
+      <c r="AT19" s="3" t="inlineStr"/>
+      <c r="AU19" s="3" t="inlineStr"/>
+      <c r="AV19" s="3" t="inlineStr"/>
+      <c r="AW19" s="3" t="inlineStr"/>
+      <c r="AX19" s="3" t="inlineStr"/>
+      <c r="AY19" s="3" t="inlineStr"/>
+      <c r="AZ19" s="3" t="inlineStr"/>
+      <c r="BA19" s="3" t="inlineStr"/>
+      <c r="BB19" s="3" t="inlineStr">
+        <is>
+          <t>CLX</t>
+        </is>
+      </c>
+      <c r="BC19" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD19" s="4" t="inlineStr"/>
-      <c r="BE19" s="4" t="inlineStr">
+      <c r="BD19" s="3" t="inlineStr"/>
+      <c r="BE19" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF19" s="4" t="inlineStr"/>
-      <c r="BG19" s="4" t="inlineStr">
+      <c r="BF19" s="3" t="inlineStr"/>
+      <c r="BG19" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH19" s="4" t="inlineStr"/>
-      <c r="BI19" s="4" t="inlineStr"/>
-      <c r="BJ19" s="4" t="inlineStr"/>
-      <c r="BK19" s="4" t="inlineStr">
+      <c r="BH19" s="3" t="inlineStr"/>
+      <c r="BI19" s="3" t="inlineStr"/>
+      <c r="BJ19" s="3" t="inlineStr"/>
+      <c r="BK19" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01T03:54:17+08:00</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>FTC and 22 States Sue Amazon Over Advertising Practices</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>'-0.938</t>
-        </is>
-      </c>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOWlU3MmpCaE01eGNlN2wzandqZjNIQlpQdXBaUFRweTVEM3RJZi1pcHE4VWs3cjZsNnh1b3cxX1FJTkJZRU9PZmNKdUJ6RXdVMThrQXpDM09ScktoUVJtc2V6dW1iNHlOTkVTT201VFRNS0JQbDBBVlFicUROYXFiUzJpdUpBZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>The New York Times</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="inlineStr"/>
-      <c r="X20" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y20" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z20" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="inlineStr">
-        <is>
-          <t>c2dd5d797110490fb8558b0b4aba1edc</t>
-        </is>
-      </c>
-      <c r="AC20" s="4" t="inlineStr">
-        <is>
-          <t>f8820d0a89ac0aed2c6dc5f0</t>
-        </is>
-      </c>
-      <c r="AD20" s="4" t="inlineStr">
-        <is>
-          <t>004b1245213be0dd4574e8a2</t>
-        </is>
-      </c>
-      <c r="AE20" s="4" t="inlineStr"/>
-      <c r="AF20" s="4" t="inlineStr"/>
-      <c r="AG20" s="4" t="inlineStr"/>
-      <c r="AH20" s="4" t="inlineStr"/>
-      <c r="AI20" s="4" t="inlineStr"/>
-      <c r="AJ20" s="4" t="inlineStr"/>
-      <c r="AK20" s="4" t="inlineStr"/>
-      <c r="AL20" s="4" t="inlineStr"/>
-      <c r="AM20" s="4" t="inlineStr"/>
-      <c r="AN20" s="4" t="inlineStr"/>
-      <c r="AO20" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP20" s="4" t="inlineStr"/>
-      <c r="AQ20" s="4" t="inlineStr"/>
-      <c r="AR20" s="4" t="inlineStr"/>
-      <c r="AS20" s="4" t="inlineStr"/>
-      <c r="AT20" s="4" t="inlineStr"/>
-      <c r="AU20" s="4" t="inlineStr"/>
-      <c r="AV20" s="4" t="inlineStr"/>
-      <c r="AW20" s="4" t="inlineStr"/>
-      <c r="AX20" s="4" t="inlineStr"/>
-      <c r="AY20" s="4" t="inlineStr"/>
-      <c r="AZ20" s="4" t="inlineStr"/>
-      <c r="BA20" s="4" t="inlineStr"/>
-      <c r="BB20" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BC20" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD20" s="4" t="inlineStr"/>
-      <c r="BE20" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF20" s="4" t="inlineStr"/>
-      <c r="BG20" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH20" s="4" t="inlineStr"/>
-      <c r="BI20" s="4" t="inlineStr"/>
-      <c r="BJ20" s="4" t="inlineStr"/>
-      <c r="BK20" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL20" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01T03:39:49+08:00</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>FTC sues Amazon, alleging it overcharged advertisers</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>'-0.934</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBLTXBWUDVyaXFnR1c0LUh4M25EYXFzUGVoYlRPYWQyZjF5alVSd2ZoaDZFcVdGaDhvRjk4d0wwRmhRSTktbzBXWER5eFJOZkMtT2tRay1qMldfRk1CM0cwTkxHa2psbzEtM1E2M29ERzlocWZS?oc=5</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="inlineStr">
-        <is>
-          <t>CNN</t>
-        </is>
-      </c>
-      <c r="W21" s="4" t="inlineStr"/>
-      <c r="X21" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y21" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z21" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="inlineStr">
-        <is>
-          <t>e0aaa3cdf81747feb03dd5a9656858c0</t>
-        </is>
-      </c>
-      <c r="AC21" s="4" t="inlineStr">
-        <is>
-          <t>2a0a25ef1ef4370eeb5a5eaa</t>
-        </is>
-      </c>
-      <c r="AD21" s="4" t="inlineStr">
-        <is>
-          <t>ad64556ce1e6d19ce0b16072</t>
-        </is>
-      </c>
-      <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="4" t="inlineStr"/>
-      <c r="AG21" s="4" t="inlineStr"/>
-      <c r="AH21" s="4" t="inlineStr"/>
-      <c r="AI21" s="4" t="inlineStr"/>
-      <c r="AJ21" s="4" t="inlineStr"/>
-      <c r="AK21" s="4" t="inlineStr"/>
-      <c r="AL21" s="4" t="inlineStr"/>
-      <c r="AM21" s="4" t="inlineStr"/>
-      <c r="AN21" s="4" t="inlineStr"/>
-      <c r="AO21" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP21" s="4" t="inlineStr"/>
-      <c r="AQ21" s="4" t="inlineStr"/>
-      <c r="AR21" s="4" t="inlineStr"/>
-      <c r="AS21" s="4" t="inlineStr"/>
-      <c r="AT21" s="4" t="inlineStr"/>
-      <c r="AU21" s="4" t="inlineStr"/>
-      <c r="AV21" s="4" t="inlineStr"/>
-      <c r="AW21" s="4" t="inlineStr"/>
-      <c r="AX21" s="4" t="inlineStr"/>
-      <c r="AY21" s="4" t="inlineStr"/>
-      <c r="AZ21" s="4" t="inlineStr"/>
-      <c r="BA21" s="4" t="inlineStr"/>
-      <c r="BB21" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BC21" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD21" s="4" t="inlineStr"/>
-      <c r="BE21" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF21" s="4" t="inlineStr"/>
-      <c r="BG21" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH21" s="4" t="inlineStr"/>
-      <c r="BI21" s="4" t="inlineStr"/>
-      <c r="BJ21" s="4" t="inlineStr"/>
-      <c r="BK21" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01T02:06:28+08:00</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>FTC聯合22州起訴亞馬遜 涉嫌從廣吿主多收數百億美元</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr"/>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="4" t="inlineStr"/>
-      <c r="R22" s="4" t="inlineStr"/>
-      <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2643055</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W22" s="4" t="inlineStr"/>
-      <c r="X22" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y22" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z22" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="inlineStr">
-        <is>
-          <t>ea9af256a8ac4be09998875709baf4ca</t>
-        </is>
-      </c>
-      <c r="AC22" s="4" t="inlineStr">
-        <is>
-          <t>b66f2435d96a4a21a118e6f6</t>
-        </is>
-      </c>
-      <c r="AD22" s="4" t="inlineStr">
-        <is>
-          <t>8143fc2d66639e2ae05eba17</t>
-        </is>
-      </c>
-      <c r="AE22" s="4" t="inlineStr"/>
-      <c r="AF22" s="4" t="inlineStr"/>
-      <c r="AG22" s="4" t="inlineStr"/>
-      <c r="AH22" s="4" t="inlineStr"/>
-      <c r="AI22" s="4" t="inlineStr"/>
-      <c r="AJ22" s="4" t="inlineStr"/>
-      <c r="AK22" s="4" t="inlineStr"/>
-      <c r="AL22" s="4" t="inlineStr"/>
-      <c r="AM22" s="4" t="inlineStr"/>
-      <c r="AN22" s="4" t="inlineStr"/>
-      <c r="AO22" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP22" s="4" t="inlineStr"/>
-      <c r="AQ22" s="4" t="inlineStr"/>
-      <c r="AR22" s="4" t="inlineStr"/>
-      <c r="AS22" s="4" t="inlineStr"/>
-      <c r="AT22" s="4" t="inlineStr"/>
-      <c r="AU22" s="4" t="inlineStr"/>
-      <c r="AV22" s="4" t="inlineStr"/>
-      <c r="AW22" s="4" t="inlineStr"/>
-      <c r="AX22" s="4" t="inlineStr"/>
-      <c r="AY22" s="4" t="inlineStr"/>
-      <c r="AZ22" s="4" t="inlineStr"/>
-      <c r="BA22" s="4" t="inlineStr"/>
-      <c r="BB22" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BC22" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD22" s="4" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BE22" s="4" t="inlineStr"/>
-      <c r="BF22" s="4" t="inlineStr"/>
-      <c r="BG22" s="4" t="inlineStr"/>
-      <c r="BH22" s="4" t="inlineStr"/>
-      <c r="BI22" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="BJ22" s="4" t="inlineStr"/>
-      <c r="BK22" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL22" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Clorox</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01T00:18:00+08:00</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Clorox Slides as Weak Demand, Margin Pressure, and Cautious FY27 Outlook Remain in Focus</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>'-0.962</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNV05aeksyZGRMRjEyT3ZMRUZQNEJzOEN0cjBLYXVmLXA2c2xiVnVfZHQ1WkJrRVQ5Z01XMm5MakRBczB4R1FXczgxY2ZESjNKWGlfT0Y0YUhub2k5ckJsQXA3WVlqZlA2aFI1SVVBNnB4RE1XRTQxZ1R5dW9KUVpZSmRuTmpSREU0aUVnVVVYS0phdHBoZG1PTnVVMTYtaERTZWo1TUR6TUJXWW1vaVJ3XzVwUFFzRmVhLWx1RUtYcWdlZzA?oc=5</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t>Quiver Quantitative</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA23" s="3" t="inlineStr"/>
-      <c r="AB23" s="3" t="inlineStr"/>
-      <c r="AC23" s="3" t="inlineStr">
-        <is>
-          <t>2f3f4a24ec42bc53e02009cc</t>
-        </is>
-      </c>
-      <c r="AD23" s="3" t="inlineStr">
-        <is>
-          <t>9cebe0a71c84871dc5c89d97</t>
-        </is>
-      </c>
-      <c r="AE23" s="3" t="inlineStr"/>
-      <c r="AF23" s="3" t="inlineStr"/>
-      <c r="AG23" s="3" t="inlineStr"/>
-      <c r="AH23" s="3" t="inlineStr"/>
-      <c r="AI23" s="3" t="inlineStr"/>
-      <c r="AJ23" s="3" t="inlineStr"/>
-      <c r="AK23" s="3" t="inlineStr"/>
-      <c r="AL23" s="3" t="inlineStr"/>
-      <c r="AM23" s="3" t="inlineStr"/>
-      <c r="AN23" s="3" t="inlineStr"/>
-      <c r="AO23" s="3" t="inlineStr"/>
-      <c r="AP23" s="3" t="inlineStr"/>
-      <c r="AQ23" s="3" t="inlineStr"/>
-      <c r="AR23" s="3" t="inlineStr"/>
-      <c r="AS23" s="3" t="inlineStr"/>
-      <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="inlineStr"/>
-      <c r="AV23" s="3" t="inlineStr"/>
-      <c r="AW23" s="3" t="inlineStr"/>
-      <c r="AX23" s="3" t="inlineStr"/>
-      <c r="AY23" s="3" t="inlineStr"/>
-      <c r="AZ23" s="3" t="inlineStr"/>
-      <c r="BA23" s="3" t="inlineStr"/>
-      <c r="BB23" s="3" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="BC23" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD23" s="3" t="inlineStr"/>
-      <c r="BE23" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF23" s="3" t="inlineStr"/>
-      <c r="BG23" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH23" s="3" t="inlineStr"/>
-      <c r="BI23" s="3" t="inlineStr"/>
-      <c r="BJ23" s="3" t="inlineStr"/>
-      <c r="BK23" s="3" t="inlineStr"/>
-      <c r="BL23" s="3" t="inlineStr"/>
+      <c r="BL19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL23"/>
+  <autoFilter ref="A1:BL19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13917,7 +13445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL5"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14308,684 +13836,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Intercontinental Exchange</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01T23:54:00+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>The Nepal and Tibet flood is a warning: melting snow and ice will bring more disasters around the world | Bill McGuire</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.622</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQMTFyaVFfZmRrTU1BcS0wTDY5NmZyYWdJek9hRTFlNVk2VG0zY3JiODlxa3VCV0JUV1pWNWJXLW1ZV1pzTDIybWZKTVpOWG1fQkkzUGF2VFIzcy1CaDdKcXh3WlJ3VDJyNkJ3T1hWWVd6bGVRa01YM28yd2F4SUdLNWl2Z1ZxaWNZVDVYOFp1ZVZOUnc5SDd3VkFwQjgzN0lvSHJUSmpvMUdmTXp0LUE?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>theguardian.com</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>flood</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>e006492205d8d22958768470</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>468f94bc12a78e89efda0cca</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Apollo Global Management</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01T22:28:35+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>阿波羅旗下的Brightspeed營收下滑，持續經營能力存疑——彭博社</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-APO/news/</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>營收下滑</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>5d43cfd57981988bfc15a325</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>1132d3c62017c03ff982a7c7</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr"/>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>APO</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="3" t="inlineStr">
-        <is>
-          <t>APO</t>
-        </is>
-      </c>
-      <c r="BE3" s="3" t="inlineStr"/>
-      <c r="BF3" s="3" t="inlineStr"/>
-      <c r="BG3" s="3" t="inlineStr"/>
-      <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
-      <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Robinhood Markets</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01T21:39:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Wildfires at Fort Hood burn 965 acres</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.391</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPb05KZmRqeVN0eHNrZU00ME55NFVOZzdXM0ZDQW93VGE5WFZlbFBXbFd0MDI1S0FHZWhBbF9zSVVJbGtyUHQ3bkRfMVJENWxMRWJPQzFJNWhNTDFSdlJkZzY4bE1Vc1NYNUtTQnNycGJDLWpYRXZHRktZN2xPbF9Oc2oyVlFacjJqazVkMlhOQ1ZJOHcxRWlSWks2WFdXdHF4clYtQVg2YjZiNVNVVzdFOFV6MmoyRE0?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>The Killeen Daily Herald</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>f2ed9f2726c5bb4fc4489405</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>66768720728d18e244880137</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr"/>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD4" s="2" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BE4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="2" t="inlineStr"/>
-      <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
-      <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Estée Lauder Companies (The)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01T18:01:51+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Reducing Indonesia wildfires will be challenging as El Niño peaks this month, minister warns</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>'-0.715</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQRUN1a1R0SmN5cTJ0SHAyMFpiOEN3bGVxdmptWlFiWVNFOVFhcGVZOC16NTBOek5Nc3JQX1N6MEkxdXJfZjZWb2tBVkN5T0h2Vm43RERNMXZrMDNzVkxfZkpDSTJXc0RTQ2xmbkNYVk81SmFESzYtSi1zdXBJVy1WZGNHeVRabm1pME05Ulh1YTJwSnJGWUM3SGtpYWVVYTA3aUlWMWJvZnlIdUlCSmFvdVM3WE01MFFFcnNjTjBndnQ3bTZ0R1ZPeA?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>203fe8e4a9d16be29b38ed3b</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>b1b55281d280636e38c53fee</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
-      <c r="AM5" s="2" t="inlineStr"/>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="inlineStr"/>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr"/>
-      <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr"/>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
-      <c r="BA5" s="2" t="inlineStr"/>
-      <c r="BB5" s="2" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="BC5" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="2" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="BE5" s="2" t="inlineStr"/>
-      <c r="BF5" s="2" t="inlineStr"/>
-      <c r="BG5" s="2" t="inlineStr"/>
-      <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
-      <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL5"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-09-01.xlsx
+++ b/news_daily/2026-09-01.xlsx
@@ -1078,28 +1078,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1139,7 +1143,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1148,7 +1152,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>4e97fa2565a54ac4b84e5aad1a80c3b8</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>36e267ca230429d8a19bda68</t>
@@ -1169,7 +1177,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1213,10 +1225,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1267,13 +1291,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1322,7 +1350,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>04b0cad648f34820b241d875c28e18e5</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>213777f2b157a7a1f5c9cd68</t>
@@ -1343,7 +1375,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1381,8 +1417,16 @@
       <c r="BH4" s="2" t="inlineStr"/>
       <c r="BI4" s="2" t="inlineStr"/>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1418,28 +1462,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1479,7 +1527,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1488,7 +1536,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>b0396c2e9c3745d39c039fa1610a55a5</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>ae6e74e274fd6fc385908d5f</t>
@@ -1509,7 +1561,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1553,10 +1609,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2534,28 +2602,32 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2595,7 +2667,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -2604,7 +2676,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>5903d81f72d54ea08fbb82f7be35fc1a</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>2e790e02d75162e1408df760</t>
@@ -2625,7 +2701,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2669,10 +2749,22 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2902,28 +2994,32 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2963,7 +3059,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2972,7 +3068,11 @@
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>ea5a045075384b4195c1a624c71b0960</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>a00aff5301106ff500f61e79</t>
@@ -2993,7 +3093,11 @@
       <c r="AL13" s="2" t="inlineStr"/>
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="2" t="inlineStr"/>
       <c r="AQ13" s="2" t="inlineStr"/>
       <c r="AR13" s="2" t="inlineStr"/>
@@ -3037,10 +3141,22 @@
         </is>
       </c>
       <c r="BH13" s="2" t="inlineStr"/>
-      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ13" s="2" t="inlineStr"/>
-      <c r="BK13" s="2" t="inlineStr"/>
-      <c r="BL13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3468,28 +3584,32 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3529,7 +3649,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -3538,7 +3658,11 @@
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>3a1577bf70d74c8f8d5d982f4586c33f</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>6daa27c4b4aa40a9c9eb349c</t>
@@ -3559,7 +3683,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3595,10 +3723,22 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
-      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -4212,28 +4352,32 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4273,7 +4417,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4282,7 +4426,11 @@
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>222f857714df497e90430dee3469e36b</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>889990a65570ae3379282aee</t>
@@ -4303,7 +4451,11 @@
       <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="2" t="inlineStr"/>
       <c r="AQ20" s="2" t="inlineStr"/>
       <c r="AR20" s="2" t="inlineStr"/>
@@ -4347,10 +4499,22 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
-      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="2" t="inlineStr"/>
-      <c r="BK20" s="2" t="inlineStr"/>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4762,28 +4926,32 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4823,7 +4991,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -4832,7 +5000,11 @@
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr"/>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>372fd51c942d40b3828b34084feda2f4</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>d06c263081c647dc8ab80e83</t>
@@ -4853,7 +5025,11 @@
       <c r="AL23" s="2" t="inlineStr"/>
       <c r="AM23" s="2" t="inlineStr"/>
       <c r="AN23" s="2" t="inlineStr"/>
-      <c r="AO23" s="2" t="inlineStr"/>
+      <c r="AO23" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP23" s="2" t="inlineStr"/>
       <c r="AQ23" s="2" t="inlineStr"/>
       <c r="AR23" s="2" t="inlineStr"/>
@@ -4897,10 +5073,22 @@
         </is>
       </c>
       <c r="BH23" s="2" t="inlineStr"/>
-      <c r="BI23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ23" s="2" t="inlineStr"/>
-      <c r="BK23" s="2" t="inlineStr"/>
-      <c r="BL23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5921,13 +6109,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5976,7 +6168,11 @@
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr"/>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>a658fee7ea13400f8492ef220b16c3e3</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
           <t>89afa6e5468c437f332d1ea0</t>
@@ -5997,7 +6193,11 @@
       <c r="AL29" s="2" t="inlineStr"/>
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr"/>
-      <c r="AO29" s="2" t="inlineStr"/>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP29" s="2" t="inlineStr"/>
       <c r="AQ29" s="2" t="inlineStr"/>
       <c r="AR29" s="2" t="inlineStr"/>
@@ -6035,8 +6235,16 @@
       <c r="BH29" s="2" t="inlineStr"/>
       <c r="BI29" s="2" t="inlineStr"/>
       <c r="BJ29" s="2" t="inlineStr"/>
-      <c r="BK29" s="2" t="inlineStr"/>
-      <c r="BL29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -6258,28 +6466,32 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6319,7 +6531,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -6328,7 +6540,11 @@
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr"/>
-      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>59a69beb54a94d519ed5f334bd4a6e57</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
           <t>26f41697aeb28dbf6f9aaddd</t>
@@ -6349,7 +6565,11 @@
       <c r="AL31" s="2" t="inlineStr"/>
       <c r="AM31" s="2" t="inlineStr"/>
       <c r="AN31" s="2" t="inlineStr"/>
-      <c r="AO31" s="2" t="inlineStr"/>
+      <c r="AO31" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP31" s="2" t="inlineStr"/>
       <c r="AQ31" s="2" t="inlineStr"/>
       <c r="AR31" s="2" t="inlineStr"/>
@@ -6393,10 +6613,22 @@
         </is>
       </c>
       <c r="BH31" s="2" t="inlineStr"/>
-      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ31" s="2" t="inlineStr"/>
-      <c r="BK31" s="2" t="inlineStr"/>
-      <c r="BL31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6432,28 +6664,32 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6493,7 +6729,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -6502,7 +6738,11 @@
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr"/>
-      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>88c804ace7634bb39868cd8212658b72</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
           <t>3e7b97d5be46fa1aea222e1d</t>
@@ -6523,7 +6763,11 @@
       <c r="AL32" s="2" t="inlineStr"/>
       <c r="AM32" s="2" t="inlineStr"/>
       <c r="AN32" s="2" t="inlineStr"/>
-      <c r="AO32" s="2" t="inlineStr"/>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP32" s="2" t="inlineStr"/>
       <c r="AQ32" s="2" t="inlineStr"/>
       <c r="AR32" s="2" t="inlineStr"/>
@@ -6567,10 +6811,22 @@
         </is>
       </c>
       <c r="BH32" s="2" t="inlineStr"/>
-      <c r="BI32" s="2" t="inlineStr"/>
+      <c r="BI32" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ32" s="2" t="inlineStr"/>
-      <c r="BK32" s="2" t="inlineStr"/>
-      <c r="BL32" s="2" t="inlineStr"/>
+      <c r="BK32" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6796,28 +7052,32 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6857,7 +7117,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -6866,7 +7126,11 @@
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr"/>
-      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>eeaf8349c20d49b88e30ac5d40610e58</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>29b0e790f9509f4e787cb72f</t>
@@ -6887,7 +7151,11 @@
       <c r="AL34" s="2" t="inlineStr"/>
       <c r="AM34" s="2" t="inlineStr"/>
       <c r="AN34" s="2" t="inlineStr"/>
-      <c r="AO34" s="2" t="inlineStr"/>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP34" s="2" t="inlineStr"/>
       <c r="AQ34" s="2" t="inlineStr"/>
       <c r="AR34" s="2" t="inlineStr"/>
@@ -6931,10 +7199,22 @@
         </is>
       </c>
       <c r="BH34" s="2" t="inlineStr"/>
-      <c r="BI34" s="2" t="inlineStr"/>
+      <c r="BI34" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ34" s="2" t="inlineStr"/>
-      <c r="BK34" s="2" t="inlineStr"/>
-      <c r="BL34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7168,28 +7448,32 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -7229,7 +7513,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -7238,7 +7522,11 @@
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr"/>
-      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>3d2aae2d144549eebca74e943d29132e</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>69be5ad84593beba39252291</t>
@@ -7259,7 +7547,11 @@
       <c r="AL36" s="2" t="inlineStr"/>
       <c r="AM36" s="2" t="inlineStr"/>
       <c r="AN36" s="2" t="inlineStr"/>
-      <c r="AO36" s="2" t="inlineStr"/>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP36" s="2" t="inlineStr"/>
       <c r="AQ36" s="2" t="inlineStr"/>
       <c r="AR36" s="2" t="inlineStr"/>
@@ -7303,10 +7595,22 @@
         </is>
       </c>
       <c r="BH36" s="2" t="inlineStr"/>
-      <c r="BI36" s="2" t="inlineStr"/>
+      <c r="BI36" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ36" s="2" t="inlineStr"/>
-      <c r="BK36" s="2" t="inlineStr"/>
-      <c r="BL36" s="2" t="inlineStr"/>
+      <c r="BK36" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7342,28 +7646,32 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -7403,7 +7711,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -7412,7 +7720,11 @@
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr"/>
-      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>1c7162b5b28c43c9b6affd914053d893</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>ea506db09f2119072c19b024</t>
@@ -7433,7 +7745,11 @@
       <c r="AL37" s="2" t="inlineStr"/>
       <c r="AM37" s="2" t="inlineStr"/>
       <c r="AN37" s="2" t="inlineStr"/>
-      <c r="AO37" s="2" t="inlineStr"/>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP37" s="2" t="inlineStr"/>
       <c r="AQ37" s="2" t="inlineStr"/>
       <c r="AR37" s="2" t="inlineStr"/>
@@ -7469,10 +7785,22 @@
         </is>
       </c>
       <c r="BH37" s="2" t="inlineStr"/>
-      <c r="BI37" s="2" t="inlineStr"/>
+      <c r="BI37" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ37" s="2" t="inlineStr"/>
-      <c r="BK37" s="2" t="inlineStr"/>
-      <c r="BL37" s="2" t="inlineStr"/>
+      <c r="BK37" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -7694,28 +8022,32 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -7755,7 +8087,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -7764,7 +8096,11 @@
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr"/>
-      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>e11fae970eb640009562493c1b416016</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>023241e2cadacadd425ac901</t>
@@ -7785,7 +8121,11 @@
       <c r="AL39" s="2" t="inlineStr"/>
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr"/>
-      <c r="AO39" s="2" t="inlineStr"/>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP39" s="2" t="inlineStr"/>
       <c r="AQ39" s="2" t="inlineStr"/>
       <c r="AR39" s="2" t="inlineStr"/>
@@ -7829,10 +8169,22 @@
         </is>
       </c>
       <c r="BH39" s="2" t="inlineStr"/>
-      <c r="BI39" s="2" t="inlineStr"/>
+      <c r="BI39" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ39" s="2" t="inlineStr"/>
-      <c r="BK39" s="2" t="inlineStr"/>
-      <c r="BL39" s="2" t="inlineStr"/>
+      <c r="BK39" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -8612,28 +8964,32 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -8673,7 +9029,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -8682,7 +9038,11 @@
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr"/>
-      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>3dd786dac8f74effb2453e2ef3599ec7</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
           <t>bddf88410fa964dd2f0315b9</t>
@@ -8703,7 +9063,11 @@
       <c r="AL44" s="2" t="inlineStr"/>
       <c r="AM44" s="2" t="inlineStr"/>
       <c r="AN44" s="2" t="inlineStr"/>
-      <c r="AO44" s="2" t="inlineStr"/>
+      <c r="AO44" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP44" s="2" t="inlineStr"/>
       <c r="AQ44" s="2" t="inlineStr"/>
       <c r="AR44" s="2" t="inlineStr"/>
@@ -8747,10 +9111,22 @@
         </is>
       </c>
       <c r="BH44" s="2" t="inlineStr"/>
-      <c r="BI44" s="2" t="inlineStr"/>
+      <c r="BI44" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ44" s="2" t="inlineStr"/>
-      <c r="BK44" s="2" t="inlineStr"/>
-      <c r="BL44" s="2" t="inlineStr"/>
+      <c r="BK44" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8786,28 +9162,32 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -8847,7 +9227,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -8856,7 +9236,11 @@
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr"/>
-      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>a4e0a91fabed4aa9a9258b2b80d9ad91</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
           <t>b70be9af8fcaf4baa76cdc69</t>
@@ -8877,7 +9261,11 @@
       <c r="AL45" s="2" t="inlineStr"/>
       <c r="AM45" s="2" t="inlineStr"/>
       <c r="AN45" s="2" t="inlineStr"/>
-      <c r="AO45" s="2" t="inlineStr"/>
+      <c r="AO45" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP45" s="2" t="inlineStr"/>
       <c r="AQ45" s="2" t="inlineStr"/>
       <c r="AR45" s="2" t="inlineStr"/>
@@ -8921,10 +9309,22 @@
         </is>
       </c>
       <c r="BH45" s="2" t="inlineStr"/>
-      <c r="BI45" s="2" t="inlineStr"/>
+      <c r="BI45" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ45" s="2" t="inlineStr"/>
-      <c r="BK45" s="2" t="inlineStr"/>
-      <c r="BL45" s="2" t="inlineStr"/>
+      <c r="BK45" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -9142,28 +9542,32 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -9203,7 +9607,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -9212,7 +9616,11 @@
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr"/>
-      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>8be60ec87a6946eb91b602c92360c60c</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
           <t>702a21c72e6182dcfab191a2</t>
@@ -9233,7 +9641,11 @@
       <c r="AL47" s="2" t="inlineStr"/>
       <c r="AM47" s="2" t="inlineStr"/>
       <c r="AN47" s="2" t="inlineStr"/>
-      <c r="AO47" s="2" t="inlineStr"/>
+      <c r="AO47" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP47" s="2" t="inlineStr"/>
       <c r="AQ47" s="2" t="inlineStr"/>
       <c r="AR47" s="2" t="inlineStr"/>
@@ -9277,10 +9689,22 @@
         </is>
       </c>
       <c r="BH47" s="2" t="inlineStr"/>
-      <c r="BI47" s="2" t="inlineStr"/>
+      <c r="BI47" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ47" s="2" t="inlineStr"/>
-      <c r="BK47" s="2" t="inlineStr"/>
-      <c r="BL47" s="2" t="inlineStr"/>
+      <c r="BK47" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9316,28 +9740,32 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -9377,7 +9805,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -9386,7 +9814,11 @@
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr"/>
-      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>ef14ec6360e14b0498c2729385be4793</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
           <t>632e2339c6b9ed4e355d328a</t>
@@ -9407,7 +9839,11 @@
       <c r="AL48" s="2" t="inlineStr"/>
       <c r="AM48" s="2" t="inlineStr"/>
       <c r="AN48" s="2" t="inlineStr"/>
-      <c r="AO48" s="2" t="inlineStr"/>
+      <c r="AO48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP48" s="2" t="inlineStr"/>
       <c r="AQ48" s="2" t="inlineStr"/>
       <c r="AR48" s="2" t="inlineStr"/>
@@ -9451,10 +9887,22 @@
         </is>
       </c>
       <c r="BH48" s="2" t="inlineStr"/>
-      <c r="BI48" s="2" t="inlineStr"/>
+      <c r="BI48" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ48" s="2" t="inlineStr"/>
-      <c r="BK48" s="2" t="inlineStr"/>
-      <c r="BL48" s="2" t="inlineStr"/>
+      <c r="BK48" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
